--- a/data/trans_orig/IP24_R2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R2_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24438</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14630</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45206</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>36,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17241</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11984</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23781</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28872</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16986</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57988</t>
+          <t>22252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46113</t>
+          <t>40435</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>29604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73915</t>
+          <t>64964</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>101050</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80282</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>110858</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>63,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>99660</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>93120</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>104917</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>85,25%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>104748</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81895</t>
+          <t>98493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122897</t>
+          <t>109684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>210670</t>
+          <t>205798</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>182868</t>
+          <t>181269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>223201</t>
+          <t>216629</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139883</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139883</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139883</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32536</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23939</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41649</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>40049</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>28850</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>55665</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21,02%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41390</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>23668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>81439</t>
+          <t>63569</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68299</t>
+          <t>52589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101247</t>
+          <t>75791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>203385</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>194272</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>211982</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,21%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>150463</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>134847</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>161662</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>78,98%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>212317</t>
+          <t>153380</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201014</t>
+          <t>144362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221937</t>
+          <t>160745</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>362781</t>
+          <t>356765</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>342973</t>
+          <t>344543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>375921</t>
+          <t>367745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>87,49%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>253707</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>253707</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>253707</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34957</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26161</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45846</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>66418</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>41509</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>118019</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30984</t>
+          <t>27071</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53759</t>
+          <t>46523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>107775</t>
+          <t>70957</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81443</t>
+          <t>58404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163562</t>
+          <t>86164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131486</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>120597</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>140282</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>123167</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>71566</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>64,97%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37,75%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>78,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>141511</t>
+          <t>120204</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129109</t>
+          <t>109681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151884</t>
+          <t>129133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>264678</t>
+          <t>251690</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>208891</t>
+          <t>236483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>291010</t>
+          <t>264243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182868</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182868</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182868</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23414</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31636</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>31687</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22664</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41509</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,99%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17407</t>
+          <t>21724</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>37514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>55569</t>
+          <t>52470</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>42158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68836</t>
+          <t>63790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>145962</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>137740</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>152225</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>135144</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>125322</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>144167</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>81,01%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>157356</t>
+          <t>137103</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147533</t>
+          <t>128646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163831</t>
+          <t>144436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>292500</t>
+          <t>283066</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279233</t>
+          <t>271746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303759</t>
+          <t>293378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>98906</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>144738</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>155395</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>124635</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>229313</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,54%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115769</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>128550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251372</t>
+          <t>204352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>362673</t>
+          <t>256861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>581884</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>552490</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>598322</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>754</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>508434</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>434516</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>539194</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,46%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>622196</t>
+          <t>515435</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>589268</t>
+          <t>498972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>641928</t>
+          <t>530485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1130630</t>
+          <t>1097319</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1058853</t>
+          <t>1067889</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1170154</t>
+          <t>1120398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
